--- a/diseases/d239/2020-2025.xlsx
+++ b/diseases/d239/2020-2025.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
@@ -1400,9 +1397,6 @@
       <c r="O5" t="n">
         <v>1</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0.0185898709184428</v>
       </c>
@@ -2035,9 +2029,6 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
@@ -2670,9 +2661,6 @@
       <c r="O11" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
@@ -3305,9 +3293,6 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
@@ -3940,9 +3925,6 @@
       <c r="O17" t="n">
         <v>1</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0.0185898709184428</v>
       </c>
@@ -4575,9 +4557,6 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
@@ -5210,9 +5189,6 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
@@ -5845,9 +5821,6 @@
       <c r="O26" t="n">
         <v>1</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.0185898709184428</v>
       </c>
@@ -6480,9 +6453,6 @@
       <c r="O29" t="n">
         <v>0</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
@@ -7115,9 +7085,6 @@
       <c r="O32" t="n">
         <v>2</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0.03717974183688559</v>
       </c>
@@ -7750,9 +7717,6 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
@@ -8385,9 +8349,6 @@
       <c r="O38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
@@ -9020,9 +8981,6 @@
       <c r="O41" t="n">
         <v>0</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
@@ -9655,9 +9613,6 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
@@ -10290,9 +10245,6 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
@@ -10925,9 +10877,6 @@
       <c r="O50" t="n">
         <v>1</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.01849081482641609</v>
       </c>
@@ -11560,9 +11509,6 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
@@ -12195,9 +12141,6 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
@@ -12830,9 +12773,6 @@
       <c r="O59" t="n">
         <v>1</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0.01849081482641609</v>
       </c>
@@ -13465,9 +13405,6 @@
       <c r="O62" t="n">
         <v>0</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
@@ -14100,9 +14037,6 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
@@ -14735,9 +14669,6 @@
       <c r="O68" t="n">
         <v>1</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0.01849081482641609</v>
       </c>
@@ -15370,9 +15301,6 @@
       <c r="O71" t="n">
         <v>1</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0.01849081482641609</v>
       </c>
@@ -16005,9 +15933,6 @@
       <c r="O74" t="n">
         <v>1</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0.01832575364890953</v>
       </c>
@@ -16640,9 +16565,6 @@
       <c r="O77" t="n">
         <v>0</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0</v>
       </c>
@@ -17275,9 +17197,6 @@
       <c r="O80" t="n">
         <v>0</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0</v>
       </c>
@@ -17910,9 +17829,6 @@
       <c r="O83" t="n">
         <v>0</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0</v>
       </c>
@@ -18545,9 +18461,6 @@
       <c r="O86" t="n">
         <v>1</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.01832575364890953</v>
       </c>
@@ -19180,9 +19093,6 @@
       <c r="O89" t="n">
         <v>1</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0.01832575364890953</v>
       </c>
@@ -19815,9 +19725,6 @@
       <c r="O92" t="n">
         <v>0</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0</v>
       </c>
@@ -20450,9 +20357,6 @@
       <c r="O95" t="n">
         <v>0</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0</v>
       </c>
@@ -21085,9 +20989,6 @@
       <c r="O98" t="n">
         <v>1</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0.01832575364890953</v>
       </c>
@@ -21720,9 +21621,6 @@
       <c r="O101" t="n">
         <v>2</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0.03665150729781906</v>
       </c>
@@ -22355,9 +22253,6 @@
       <c r="O104" t="n">
         <v>0</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0</v>
       </c>
@@ -22990,9 +22885,6 @@
       <c r="O107" t="n">
         <v>2</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0.03665150729781906</v>
       </c>
@@ -23625,9 +23517,6 @@
       <c r="O110" t="n">
         <v>0</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0</v>
       </c>
@@ -24260,9 +24149,6 @@
       <c r="O113" t="n">
         <v>0</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0</v>
       </c>
@@ -24895,9 +24781,6 @@
       <c r="O116" t="n">
         <v>0</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0</v>
       </c>
@@ -25530,9 +25413,6 @@
       <c r="O119" t="n">
         <v>0</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0</v>
       </c>
@@ -26165,9 +26045,6 @@
       <c r="O122" t="n">
         <v>0</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0</v>
       </c>
@@ -26800,9 +26677,6 @@
       <c r="O125" t="n">
         <v>1</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0.01811867624226627</v>
       </c>
@@ -27435,9 +27309,6 @@
       <c r="O128" t="n">
         <v>0</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0</v>
       </c>
@@ -28070,9 +27941,6 @@
       <c r="O131" t="n">
         <v>0</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0</v>
       </c>
@@ -28705,9 +28573,6 @@
       <c r="O134" t="n">
         <v>0</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0</v>
       </c>
@@ -29340,9 +29205,6 @@
       <c r="O137" t="n">
         <v>1</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>0.01811867624226627</v>
       </c>
@@ -29975,9 +29837,6 @@
       <c r="O140" t="n">
         <v>0</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0</v>
       </c>
@@ -30610,9 +30469,6 @@
       <c r="O143" t="n">
         <v>3</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>0.05435602872679881</v>
       </c>
@@ -31245,9 +31101,6 @@
       <c r="O146" t="n">
         <v>0</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0</v>
       </c>
@@ -31880,9 +31733,6 @@
       <c r="O149" t="n">
         <v>5</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0.08965940186419828</v>
       </c>
@@ -32515,9 +32365,6 @@
       <c r="O152" t="n">
         <v>2</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0.03586376074567932</v>
       </c>
@@ -33150,9 +32997,6 @@
       <c r="O155" t="n">
         <v>0</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0</v>
       </c>
@@ -33785,9 +33629,6 @@
       <c r="O158" t="n">
         <v>0</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0</v>
       </c>
@@ -34420,9 +34261,6 @@
       <c r="O161" t="n">
         <v>0</v>
       </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
       <c r="R161" t="n">
         <v>0</v>
       </c>
@@ -35055,9 +34893,6 @@
       <c r="O164" t="n">
         <v>0</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>0</v>
       </c>
@@ -35690,9 +35525,6 @@
       <c r="O167" t="n">
         <v>2</v>
       </c>
-      <c r="Q167" t="n">
-        <v>0</v>
-      </c>
       <c r="R167" t="n">
         <v>0.03586376074567932</v>
       </c>
@@ -36325,9 +36157,6 @@
       <c r="O170" t="n">
         <v>0</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>0</v>
       </c>
@@ -36960,9 +36789,6 @@
       <c r="O173" t="n">
         <v>0</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="R173" t="n">
         <v>0</v>
       </c>
@@ -37595,9 +37421,6 @@
       <c r="O176" t="n">
         <v>1</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>0.01793188037283966</v>
       </c>
@@ -38230,9 +38053,6 @@
       <c r="O179" t="n">
         <v>2</v>
       </c>
-      <c r="Q179" t="n">
-        <v>0</v>
-      </c>
       <c r="R179" t="n">
         <v>0.03586376074567932</v>
       </c>
@@ -38865,9 +38685,6 @@
       <c r="O182" t="n">
         <v>3</v>
       </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
       <c r="R182" t="n">
         <v>0.05335162938543725</v>
       </c>
@@ -39261,9 +39078,6 @@
       <c r="O184" t="n">
         <v>17</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="R184" t="n">
         <v>0.159525058243068</v>
       </c>
@@ -39667,9 +39481,6 @@
       <c r="O186" t="n">
         <v>3</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>0.05335162938543725</v>
       </c>
@@ -40063,9 +39874,6 @@
       <c r="O188" t="n">
         <v>23</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="R188" t="n">
         <v>0.2158280199759155</v>
       </c>
@@ -40469,9 +40277,6 @@
       <c r="O190" t="n">
         <v>4</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>0.07113550584724966</v>
       </c>
@@ -40865,9 +40670,6 @@
       <c r="O192" t="n">
         <v>26</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>0.2439795008423392</v>
       </c>
@@ -41271,9 +41073,6 @@
       <c r="O194" t="n">
         <v>6</v>
       </c>
-      <c r="Q194" t="n">
-        <v>0</v>
-      </c>
       <c r="R194" t="n">
         <v>0.1067032587708745</v>
       </c>
@@ -41667,9 +41466,6 @@
       <c r="O196" t="n">
         <v>26</v>
       </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
       <c r="R196" t="n">
         <v>0.2439795008423392</v>
       </c>
@@ -42073,9 +41869,6 @@
       <c r="O198" t="n">
         <v>3</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>0.05335162938543725</v>
       </c>
@@ -42469,9 +42262,6 @@
       <c r="O200" t="n">
         <v>18</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="R200" t="n">
         <v>0.1689088851985425</v>
       </c>
@@ -42875,9 +42665,6 @@
       <c r="O202" t="n">
         <v>1</v>
       </c>
-      <c r="Q202" t="n">
-        <v>0</v>
-      </c>
       <c r="R202" t="n">
         <v>0.01778387646181242</v>
       </c>
@@ -43271,9 +43058,6 @@
       <c r="O204" t="n">
         <v>15</v>
       </c>
-      <c r="Q204" t="n">
-        <v>0</v>
-      </c>
       <c r="R204" t="n">
         <v>0.1407574043321188</v>
       </c>
@@ -43677,9 +43461,6 @@
       <c r="O206" t="n">
         <v>3</v>
       </c>
-      <c r="Q206" t="n">
-        <v>0</v>
-      </c>
       <c r="R206" t="n">
         <v>0.05335162938543725</v>
       </c>
@@ -44073,9 +43854,6 @@
       <c r="O208" t="n">
         <v>19</v>
       </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
       <c r="R208" t="n">
         <v>0.1782927121540171</v>
       </c>
@@ -44479,9 +44257,6 @@
       <c r="O210" t="n">
         <v>0</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="R210" t="n">
         <v>0</v>
       </c>
@@ -44875,9 +44650,6 @@
       <c r="O212" t="n">
         <v>10</v>
       </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
       <c r="R212" t="n">
         <v>0.09383826955474586</v>
       </c>
@@ -45281,9 +45053,6 @@
       <c r="O214" t="n">
         <v>2</v>
       </c>
-      <c r="Q214" t="n">
-        <v>0</v>
-      </c>
       <c r="R214" t="n">
         <v>0.03556775292362483</v>
       </c>
@@ -45677,9 +45446,6 @@
       <c r="O216" t="n">
         <v>13</v>
       </c>
-      <c r="Q216" t="n">
-        <v>0</v>
-      </c>
       <c r="R216" t="n">
         <v>0.1219897504211696</v>
       </c>
@@ -46083,9 +45849,6 @@
       <c r="O218" t="n">
         <v>2</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="R218" t="n">
         <v>0.03556775292362483</v>
       </c>
@@ -46479,9 +46242,6 @@
       <c r="O220" t="n">
         <v>15</v>
       </c>
-      <c r="Q220" t="n">
-        <v>0</v>
-      </c>
       <c r="R220" t="n">
         <v>0.1407574043321188</v>
       </c>
@@ -46885,9 +46645,6 @@
       <c r="O222" t="n">
         <v>7</v>
       </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
       <c r="R222" t="n">
         <v>0.1244871352326869</v>
       </c>
@@ -47281,9 +47038,6 @@
       <c r="O224" t="n">
         <v>14</v>
       </c>
-      <c r="Q224" t="n">
-        <v>0</v>
-      </c>
       <c r="R224" t="n">
         <v>0.1313735773766442</v>
       </c>
@@ -47687,9 +47441,6 @@
       <c r="O226" t="n">
         <v>3</v>
       </c>
-      <c r="Q226" t="n">
-        <v>0</v>
-      </c>
       <c r="R226" t="n">
         <v>0.05335162938543725</v>
       </c>
@@ -48082,9 +47833,6 @@
       </c>
       <c r="O228" t="n">
         <v>15</v>
-      </c>
-      <c r="Q228" t="n">
-        <v>0</v>
       </c>
       <c r="R228" t="n">
         <v>0.1407574043321188</v>
